--- a/data/nzd0394/nzd0394.xlsx
+++ b/data/nzd0394/nzd0394.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I433"/>
+  <dimension ref="A1:I436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14711,6 +14711,105 @@
         <v>360.42</v>
       </c>
       <c r="I433" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:07:01+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="n">
+        <v>359.34</v>
+      </c>
+      <c r="C434" t="n">
+        <v>345.7</v>
+      </c>
+      <c r="D434" t="n">
+        <v>347.02</v>
+      </c>
+      <c r="E434" t="n">
+        <v>340.69</v>
+      </c>
+      <c r="F434" t="n">
+        <v>334.98</v>
+      </c>
+      <c r="G434" t="n">
+        <v>348.55</v>
+      </c>
+      <c r="H434" t="n">
+        <v>360.07</v>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="n">
+        <v>359.1</v>
+      </c>
+      <c r="C435" t="n">
+        <v>346.12</v>
+      </c>
+      <c r="D435" t="n">
+        <v>347.27</v>
+      </c>
+      <c r="E435" t="n">
+        <v>340.74</v>
+      </c>
+      <c r="F435" t="n">
+        <v>336.35</v>
+      </c>
+      <c r="G435" t="n">
+        <v>349.51</v>
+      </c>
+      <c r="H435" t="n">
+        <v>361.19</v>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="n">
+        <v>358.67</v>
+      </c>
+      <c r="C436" t="n">
+        <v>346.08</v>
+      </c>
+      <c r="D436" t="n">
+        <v>347.61</v>
+      </c>
+      <c r="E436" t="n">
+        <v>341.24</v>
+      </c>
+      <c r="F436" t="n">
+        <v>336.74</v>
+      </c>
+      <c r="G436" t="n">
+        <v>349.35</v>
+      </c>
+      <c r="H436" t="n">
+        <v>361.31</v>
+      </c>
+      <c r="I436" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14727,7 +14826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B441"/>
+  <dimension ref="A1:B444"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19140,6 +19239,36 @@
       </c>
       <c r="B441" t="n">
         <v>0.11</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B442" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B443" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B444" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -19308,28 +19437,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>1.356042931693734</v>
+        <v>1.350260007333989</v>
       </c>
       <c r="J2" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K2" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5440841380566452</v>
+        <v>0.5452142850109856</v>
       </c>
       <c r="M2" t="n">
-        <v>7.741035158688769</v>
+        <v>7.719000146535657</v>
       </c>
       <c r="N2" t="n">
-        <v>91.68800780735275</v>
+        <v>91.18967070081308</v>
       </c>
       <c r="O2" t="n">
-        <v>9.575385517427105</v>
+        <v>9.549328285320025</v>
       </c>
       <c r="P2" t="n">
-        <v>326.8598388352625</v>
+        <v>326.9205685949397</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19386,28 +19515,28 @@
         <v>0.1522</v>
       </c>
       <c r="I3" t="n">
-        <v>1.658755062620589</v>
+        <v>1.650379891493507</v>
       </c>
       <c r="J3" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K3" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L3" t="n">
-        <v>0.684873531798285</v>
+        <v>0.6850051821407386</v>
       </c>
       <c r="M3" t="n">
-        <v>7.243767841679451</v>
+        <v>7.251056690203862</v>
       </c>
       <c r="N3" t="n">
-        <v>75.88532638654335</v>
+        <v>75.64979934318708</v>
       </c>
       <c r="O3" t="n">
-        <v>8.711218421469143</v>
+        <v>8.697689310569048</v>
       </c>
       <c r="P3" t="n">
-        <v>307.6530952925246</v>
+        <v>307.7405522517365</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19464,28 +19593,28 @@
         <v>0.1076</v>
       </c>
       <c r="I4" t="n">
-        <v>1.572812882173112</v>
+        <v>1.566823076478558</v>
       </c>
       <c r="J4" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K4" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6750436825202473</v>
+        <v>0.6761054051801316</v>
       </c>
       <c r="M4" t="n">
-        <v>6.767773431300207</v>
+        <v>6.76432936893243</v>
       </c>
       <c r="N4" t="n">
-        <v>71.37826815078107</v>
+        <v>71.03290768162505</v>
       </c>
       <c r="O4" t="n">
-        <v>8.448566041097214</v>
+        <v>8.428102258612258</v>
       </c>
       <c r="P4" t="n">
-        <v>309.4492011547519</v>
+        <v>309.5117468620742</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19542,28 +19671,28 @@
         <v>0.1482</v>
       </c>
       <c r="I5" t="n">
-        <v>1.183751349081405</v>
+        <v>1.182556398154722</v>
       </c>
       <c r="J5" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K5" t="n">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6896272279448465</v>
+        <v>0.6922700354223188</v>
       </c>
       <c r="M5" t="n">
-        <v>4.812085360332468</v>
+        <v>4.787499968394676</v>
       </c>
       <c r="N5" t="n">
-        <v>37.80149473883527</v>
+        <v>37.54640485721777</v>
       </c>
       <c r="O5" t="n">
-        <v>6.148292018018929</v>
+        <v>6.127512126239961</v>
       </c>
       <c r="P5" t="n">
-        <v>309.8195698844459</v>
+        <v>309.8320447446776</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19620,28 +19749,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.024011125806215</v>
+        <v>1.023507936599644</v>
       </c>
       <c r="J6" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K6" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6724726323979203</v>
+        <v>0.6754316922486708</v>
       </c>
       <c r="M6" t="n">
-        <v>4.375499471899432</v>
+        <v>4.349740912963753</v>
       </c>
       <c r="N6" t="n">
-        <v>30.38990561470367</v>
+        <v>30.18410863733127</v>
       </c>
       <c r="O6" t="n">
-        <v>5.512704020233961</v>
+        <v>5.494006610601344</v>
       </c>
       <c r="P6" t="n">
-        <v>308.7287581603125</v>
+        <v>308.7340311760785</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19698,28 +19827,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8000419529777772</v>
+        <v>0.8000672831964789</v>
       </c>
       <c r="J7" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K7" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07477800109110544</v>
+        <v>0.07579289022924707</v>
       </c>
       <c r="M7" t="n">
-        <v>9.506007704876181</v>
+        <v>9.442964177339983</v>
       </c>
       <c r="N7" t="n">
-        <v>478.1393321958899</v>
+        <v>474.842972929666</v>
       </c>
       <c r="O7" t="n">
-        <v>21.86639733005622</v>
+        <v>21.79089197186903</v>
       </c>
       <c r="P7" t="n">
-        <v>327.4873632165166</v>
+        <v>327.487096006082</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19776,28 +19905,28 @@
         <v>0.0565</v>
       </c>
       <c r="I8" t="n">
-        <v>1.915336441491705</v>
+        <v>1.905652164883377</v>
       </c>
       <c r="J8" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="K8" t="n">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6830452026855587</v>
+        <v>0.6831874331268342</v>
       </c>
       <c r="M8" t="n">
-        <v>7.951753883073239</v>
+        <v>7.965557107533996</v>
       </c>
       <c r="N8" t="n">
-        <v>101.2943094386837</v>
+        <v>100.9766702524326</v>
       </c>
       <c r="O8" t="n">
-        <v>10.06450741162645</v>
+        <v>10.04871485576303</v>
       </c>
       <c r="P8" t="n">
-        <v>316.5850145835935</v>
+        <v>316.6866989113944</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19835,7 +19964,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I433"/>
+  <dimension ref="A1:I436"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40153,6 +40282,147 @@
         </is>
       </c>
     </row>
+    <row r="434">
+      <c r="A434" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:07:01+00:00</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>-42.47747183226008,173.5319703634117</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>-42.47784801846962,173.5312118495344</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>-42.47831997827593,173.53058113542673</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>-42.47876235629019,173.52990140205208</t>
+        </is>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>-42.479295290178236,173.52933701264848</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>-42.47993254331151,173.52907694572195</t>
+        </is>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-42.480600973869244,173.5290919339398</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-12 22:07:11+00:00</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>-42.47747029522678,173.53196831064523</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>-42.47785070829487,173.53121544187434</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>-42.478321552365095,173.5305833100129</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr">
+        <is>
+          <t>-42.47876263559016,173.5299018791963</t>
+        </is>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>-42.47930148460031,173.52935142730115</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>-42.479935098692174,173.52908810351266</t>
+        </is>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-42.4806023180232,173.5291054387917</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:00+00:00</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>-42.4774675413754,173.53196463277226</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>-42.47785045212103,173.5312150997467</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>-42.47832369312629,173.5305862674503</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr">
+        <is>
+          <t>-42.47876542858984,173.52990665063902</t>
+        </is>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>-42.4793032479756,173.52935553074295</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>-42.47993467279548,173.52908624388084</t>
+        </is>
+      </c>
+      <c r="H436" t="inlineStr">
+        <is>
+          <t>-42.480602462039606,173.52910688574016</t>
+        </is>
+      </c>
+      <c r="I436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0394/nzd0394.xlsx
+++ b/data/nzd0394/nzd0394.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I436"/>
+  <dimension ref="A1:I438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14810,6 +14810,72 @@
         <v>361.31</v>
       </c>
       <c r="I436" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="n">
+        <v>359.17</v>
+      </c>
+      <c r="C437" t="n">
+        <v>346.52</v>
+      </c>
+      <c r="D437" t="n">
+        <v>348.14</v>
+      </c>
+      <c r="E437" t="n">
+        <v>341.95</v>
+      </c>
+      <c r="F437" t="n">
+        <v>336.95</v>
+      </c>
+      <c r="G437" t="n">
+        <v>349.83</v>
+      </c>
+      <c r="H437" t="n">
+        <v>361.88</v>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="n">
+        <v>359.33</v>
+      </c>
+      <c r="C438" t="n">
+        <v>347.03</v>
+      </c>
+      <c r="D438" t="n">
+        <v>348.44</v>
+      </c>
+      <c r="E438" t="n">
+        <v>342.24</v>
+      </c>
+      <c r="F438" t="n">
+        <v>337.1</v>
+      </c>
+      <c r="G438" t="n">
+        <v>350.29</v>
+      </c>
+      <c r="H438" t="n">
+        <v>362.67</v>
+      </c>
+      <c r="I438" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14826,7 +14892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B444"/>
+  <dimension ref="A1:B446"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19269,6 +19335,26 @@
       </c>
       <c r="B444" t="n">
         <v>-0.55</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B445" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B446" t="n">
+        <v>-0.38</v>
       </c>
     </row>
   </sheetData>
@@ -19437,28 +19523,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>1.350260007333989</v>
+        <v>1.346590063416384</v>
       </c>
       <c r="J2" t="n">
+        <v>437</v>
+      </c>
+      <c r="K2" t="n">
         <v>435</v>
       </c>
-      <c r="K2" t="n">
-        <v>433</v>
-      </c>
       <c r="L2" t="n">
-        <v>0.5452142850109856</v>
+        <v>0.5460330087724837</v>
       </c>
       <c r="M2" t="n">
-        <v>7.719000146535657</v>
+        <v>7.703355864727199</v>
       </c>
       <c r="N2" t="n">
-        <v>91.18967070081308</v>
+        <v>90.8539858478738</v>
       </c>
       <c r="O2" t="n">
-        <v>9.549328285320025</v>
+        <v>9.531735720626846</v>
       </c>
       <c r="P2" t="n">
-        <v>326.9205685949397</v>
+        <v>326.9592647416057</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19515,28 +19601,28 @@
         <v>0.1522</v>
       </c>
       <c r="I3" t="n">
-        <v>1.650379891493507</v>
+        <v>1.64550940078934</v>
       </c>
       <c r="J3" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K3" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6850051821407386</v>
+        <v>0.6853825220987633</v>
       </c>
       <c r="M3" t="n">
-        <v>7.251056690203862</v>
+        <v>7.250820954951028</v>
       </c>
       <c r="N3" t="n">
-        <v>75.64979934318708</v>
+        <v>75.45172146242432</v>
       </c>
       <c r="O3" t="n">
-        <v>8.697689310569048</v>
+        <v>8.686295036574817</v>
       </c>
       <c r="P3" t="n">
-        <v>307.7405522517365</v>
+        <v>307.7916223062811</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19593,28 +19679,28 @@
         <v>0.1076</v>
       </c>
       <c r="I4" t="n">
-        <v>1.566823076478558</v>
+        <v>1.563661119854786</v>
       </c>
       <c r="J4" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K4" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6761054051801316</v>
+        <v>0.6771358015096636</v>
       </c>
       <c r="M4" t="n">
-        <v>6.76432936893243</v>
+        <v>6.756145085213334</v>
       </c>
       <c r="N4" t="n">
-        <v>71.03290768162505</v>
+        <v>70.76980292879585</v>
       </c>
       <c r="O4" t="n">
-        <v>8.428102258612258</v>
+        <v>8.412479000199397</v>
       </c>
       <c r="P4" t="n">
-        <v>309.5117468620742</v>
+        <v>309.5449023539139</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19671,28 +19757,28 @@
         <v>0.1482</v>
       </c>
       <c r="I5" t="n">
-        <v>1.182556398154722</v>
+        <v>1.182711793626005</v>
       </c>
       <c r="J5" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K5" t="n">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6922700354223188</v>
+        <v>0.6943736762728905</v>
       </c>
       <c r="M5" t="n">
-        <v>4.787499968394676</v>
+        <v>4.766067805000125</v>
       </c>
       <c r="N5" t="n">
-        <v>37.54640485721777</v>
+        <v>37.37437694736592</v>
       </c>
       <c r="O5" t="n">
-        <v>6.127512126239961</v>
+        <v>6.113458673072545</v>
       </c>
       <c r="P5" t="n">
-        <v>309.8320447446776</v>
+        <v>309.8304138080622</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19749,28 +19835,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.023507936599644</v>
+        <v>1.023956195229575</v>
       </c>
       <c r="J6" t="n">
+        <v>437</v>
+      </c>
+      <c r="K6" t="n">
         <v>435</v>
       </c>
-      <c r="K6" t="n">
-        <v>433</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.6754316922486708</v>
+        <v>0.6777292936266563</v>
       </c>
       <c r="M6" t="n">
-        <v>4.349740912963753</v>
+        <v>4.331683131074696</v>
       </c>
       <c r="N6" t="n">
-        <v>30.18410863733127</v>
+        <v>30.04658544962803</v>
       </c>
       <c r="O6" t="n">
-        <v>5.494006610601344</v>
+        <v>5.481476575670833</v>
       </c>
       <c r="P6" t="n">
-        <v>308.7340311760785</v>
+        <v>308.7293040793445</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19827,28 +19913,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8000672831964789</v>
+        <v>0.8008022284016496</v>
       </c>
       <c r="J7" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="K7" t="n">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07579289022924707</v>
+        <v>0.07659784460437291</v>
       </c>
       <c r="M7" t="n">
-        <v>9.442964177339983</v>
+        <v>9.399916231472965</v>
       </c>
       <c r="N7" t="n">
-        <v>474.842972929666</v>
+        <v>472.673381391963</v>
       </c>
       <c r="O7" t="n">
-        <v>21.79089197186903</v>
+        <v>21.74105290440099</v>
       </c>
       <c r="P7" t="n">
-        <v>327.487096006082</v>
+        <v>327.4794289829737</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19905,28 +19991,28 @@
         <v>0.0565</v>
       </c>
       <c r="I8" t="n">
-        <v>1.905652164883377</v>
+        <v>1.900436885467657</v>
       </c>
       <c r="J8" t="n">
+        <v>437</v>
+      </c>
+      <c r="K8" t="n">
         <v>435</v>
       </c>
-      <c r="K8" t="n">
-        <v>433</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.6831874331268342</v>
+        <v>0.6837286818164983</v>
       </c>
       <c r="M8" t="n">
-        <v>7.965557107533996</v>
+        <v>7.965649869825721</v>
       </c>
       <c r="N8" t="n">
-        <v>100.9766702524326</v>
+        <v>100.6817389626349</v>
       </c>
       <c r="O8" t="n">
-        <v>10.04871485576303</v>
+        <v>10.03402904932186</v>
       </c>
       <c r="P8" t="n">
-        <v>316.6866989113944</v>
+        <v>316.7416853617855</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -19964,7 +20050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I436"/>
+  <dimension ref="A1:I438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40423,6 +40509,100 @@
         </is>
       </c>
     </row>
+    <row r="437">
+      <c r="A437" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:06:52+00:00</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>-42.477470743528166,173.53196890936877</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>-42.47785327003309,173.53121886315077</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>-42.478327030195054,173.53059087757367</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr">
+        <is>
+          <t>-42.47876939464901,173.52991342608837</t>
+        </is>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>-42.47930419748531,173.52935774028862</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>-42.479935950485476,173.52909182277642</t>
+        </is>
+      </c>
+      <c r="H437" t="inlineStr">
+        <is>
+          <t>-42.48060314611726,173.52911375874538</t>
+        </is>
+      </c>
+      <c r="I437" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-29 22:07:07+00:00</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>-42.477471768217015,173.53197027787974</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>-42.47785653624918,173.53122322527858</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>-42.478328919101806,173.53059348707768</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr">
+        <is>
+          <t>-42.47877101458856,173.5299161935257</t>
+        </is>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>-42.47930487570651,173.5293593185356</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>-42.47993717493816,173.52909716921826</t>
+        </is>
+      </c>
+      <c r="H438" t="inlineStr">
+        <is>
+          <t>-42.4806040942242,173.5291232844897</t>
+        </is>
+      </c>
+      <c r="I438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0394/nzd0394.xlsx
+++ b/data/nzd0394/nzd0394.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I438"/>
+  <dimension ref="A1:I439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14876,6 +14876,39 @@
         <v>362.67</v>
       </c>
       <c r="I438" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="n">
+        <v>359.14</v>
+      </c>
+      <c r="C439" t="n">
+        <v>347.34</v>
+      </c>
+      <c r="D439" t="n">
+        <v>348.44</v>
+      </c>
+      <c r="E439" t="n">
+        <v>342.26</v>
+      </c>
+      <c r="F439" t="n">
+        <v>337.27</v>
+      </c>
+      <c r="G439" t="n">
+        <v>350.47</v>
+      </c>
+      <c r="H439" t="n">
+        <v>362.56</v>
+      </c>
+      <c r="I439" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -14892,7 +14925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B446"/>
+  <dimension ref="A1:B447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19355,6 +19388,16 @@
       </c>
       <c r="B446" t="n">
         <v>-0.38</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B447" t="n">
+        <v>0.21</v>
       </c>
     </row>
   </sheetData>
@@ -19523,28 +19566,28 @@
         <v>0.0529</v>
       </c>
       <c r="I2" t="n">
-        <v>1.346590063416384</v>
+        <v>1.344690337387521</v>
       </c>
       <c r="J2" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K2" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5460330087724837</v>
+        <v>0.546407364121992</v>
       </c>
       <c r="M2" t="n">
-        <v>7.703355864727199</v>
+        <v>7.695863687236059</v>
       </c>
       <c r="N2" t="n">
-        <v>90.8539858478738</v>
+        <v>90.69063578677485</v>
       </c>
       <c r="O2" t="n">
-        <v>9.531735720626846</v>
+        <v>9.523163118773869</v>
       </c>
       <c r="P2" t="n">
-        <v>326.9592647416057</v>
+        <v>326.9793652853451</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19601,28 +19644,28 @@
         <v>0.1522</v>
       </c>
       <c r="I3" t="n">
-        <v>1.64550940078934</v>
+        <v>1.643296186727108</v>
       </c>
       <c r="J3" t="n">
+        <v>438</v>
+      </c>
+      <c r="K3" t="n">
         <v>437</v>
       </c>
-      <c r="K3" t="n">
-        <v>436</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.6853825220987633</v>
+        <v>0.6856635940586853</v>
       </c>
       <c r="M3" t="n">
-        <v>7.250820954951028</v>
+        <v>7.249114343661496</v>
       </c>
       <c r="N3" t="n">
-        <v>75.45172146242432</v>
+        <v>75.34081708758333</v>
       </c>
       <c r="O3" t="n">
-        <v>8.686295036574817</v>
+        <v>8.679908817930251</v>
       </c>
       <c r="P3" t="n">
-        <v>307.7916223062811</v>
+        <v>307.8149114180014</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19679,28 +19722,28 @@
         <v>0.1076</v>
       </c>
       <c r="I4" t="n">
-        <v>1.563661119854786</v>
+        <v>1.56211612701763</v>
       </c>
       <c r="J4" t="n">
+        <v>438</v>
+      </c>
+      <c r="K4" t="n">
         <v>437</v>
       </c>
-      <c r="K4" t="n">
-        <v>436</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.6771358015096636</v>
+        <v>0.6776629791780253</v>
       </c>
       <c r="M4" t="n">
-        <v>6.756145085213334</v>
+        <v>6.751754656495689</v>
       </c>
       <c r="N4" t="n">
-        <v>70.76980292879585</v>
+        <v>70.6379517081191</v>
       </c>
       <c r="O4" t="n">
-        <v>8.412479000199397</v>
+        <v>8.404638701819318</v>
       </c>
       <c r="P4" t="n">
-        <v>309.5449023539139</v>
+        <v>309.5611599366781</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19757,28 +19800,28 @@
         <v>0.1482</v>
       </c>
       <c r="I5" t="n">
-        <v>1.182711793626005</v>
+        <v>1.182822080135309</v>
       </c>
       <c r="J5" t="n">
+        <v>438</v>
+      </c>
+      <c r="K5" t="n">
         <v>437</v>
       </c>
-      <c r="K5" t="n">
-        <v>436</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.6943736762728905</v>
+        <v>0.695433309836059</v>
       </c>
       <c r="M5" t="n">
-        <v>4.766067805000125</v>
+        <v>4.75553341476248</v>
       </c>
       <c r="N5" t="n">
-        <v>37.37437694736592</v>
+        <v>37.28900540006691</v>
       </c>
       <c r="O5" t="n">
-        <v>6.113458673072545</v>
+        <v>6.106472418677326</v>
       </c>
       <c r="P5" t="n">
-        <v>309.8304138080622</v>
+        <v>309.8292532900263</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -19835,28 +19878,28 @@
         <v>0.2</v>
       </c>
       <c r="I6" t="n">
-        <v>1.023956195229575</v>
+        <v>1.024248160370019</v>
       </c>
       <c r="J6" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K6" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6777292936266563</v>
+        <v>0.6789000037715953</v>
       </c>
       <c r="M6" t="n">
-        <v>4.331683131074696</v>
+        <v>4.323000403256265</v>
       </c>
       <c r="N6" t="n">
-        <v>30.04658544962803</v>
+        <v>29.97873488694244</v>
       </c>
       <c r="O6" t="n">
-        <v>5.481476575670833</v>
+        <v>5.475284000574074</v>
       </c>
       <c r="P6" t="n">
-        <v>308.7293040793445</v>
+        <v>308.726214866486</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -19913,28 +19956,28 @@
         <v>0.2</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8008022284016496</v>
+        <v>0.8013107497128938</v>
       </c>
       <c r="J7" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K7" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07659784460437291</v>
+        <v>0.07702783053164886</v>
       </c>
       <c r="M7" t="n">
-        <v>9.399916231472965</v>
+        <v>9.378555185987619</v>
       </c>
       <c r="N7" t="n">
-        <v>472.673381391963</v>
+        <v>471.597512049681</v>
       </c>
       <c r="O7" t="n">
-        <v>21.74105290440099</v>
+        <v>21.71629600207367</v>
       </c>
       <c r="P7" t="n">
-        <v>327.4794289829737</v>
+        <v>327.4741072790902</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -19991,28 +20034,28 @@
         <v>0.0565</v>
       </c>
       <c r="I8" t="n">
-        <v>1.900436885467657</v>
+        <v>1.89792625808927</v>
       </c>
       <c r="J8" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="K8" t="n">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6837286818164983</v>
+        <v>0.6840321999315451</v>
       </c>
       <c r="M8" t="n">
-        <v>7.965649869825721</v>
+        <v>7.964971680069211</v>
       </c>
       <c r="N8" t="n">
-        <v>100.6817389626349</v>
+        <v>100.5294660889351</v>
       </c>
       <c r="O8" t="n">
-        <v>10.03402904932186</v>
+        <v>10.02643835511569</v>
       </c>
       <c r="P8" t="n">
-        <v>316.7416853617855</v>
+        <v>316.7682497056257</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -20050,7 +20093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I438"/>
+  <dimension ref="A1:I439"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40603,6 +40646,53 @@
         </is>
       </c>
     </row>
+    <row r="439">
+      <c r="A439" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:12+00:00</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>-42.477470551399016,173.53196865277297</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>-42.477858521596126,173.53122587676827</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>-42.478328919101806,173.53059348707768</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr">
+        <is>
+          <t>-42.478771126308516,173.52991638438345</t>
+        </is>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>-42.47930564435716,173.5293611072155</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>-42.47993765407175,173.52909926130425</t>
+        </is>
+      </c>
+      <c r="H439" t="inlineStr">
+        <is>
+          <t>-42.48060396220936,173.52912195812024</t>
+        </is>
+      </c>
+      <c r="I439" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
